--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_monthly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_xgb_monthly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>1.602643947220918</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1040,27 +1041,27 @@
         <v>0.837551214756322</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
@@ -1068,7 +1069,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1076,15 +1077,15 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1189,51 +1190,51 @@
         <v>0.8779797002427745</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1342,51 +1343,51 @@
         <v>0.8375512147563224</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="n">
@@ -1394,7 +1395,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AR6" s="3" t="n">
@@ -1402,7 +1403,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
@@ -1410,7 +1411,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
     </row>
@@ -1509,51 +1510,51 @@
         <v>1.13038219549501</v>
       </c>
       <c r="AD7" s="3" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>4/7</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>5/7</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AF7" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1662,59 +1663,59 @@
         <v>1.014226453356257</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR8" s="3" t="n">
@@ -1722,15 +1723,15 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
     </row>
@@ -1829,11 +1830,11 @@
         <v>0.3461833023210537</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
@@ -1841,23 +1842,23 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
@@ -1865,15 +1866,15 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1982,59 +1983,59 @@
         <v>0.9883044150852032</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>7/7</t>
         </is>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP10" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AR10" s="3" t="n">
@@ -2042,15 +2043,15 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>0/7</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
     </row>
@@ -2349,66 +2350,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.0903200482301444</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078731</v>
+        <v>0.04076898034342899</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582909292</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791236</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.486230944244141</v>
+        <v>-0.1697286534192365</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493482</v>
+        <v>0.2044255219913533</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2456,34 +2459,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37538</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38957</v>
+        <v>36119</v>
       </c>
       <c r="M3" t="n">
-        <v>1616</v>
+        <v>89</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="P3" t="n">
-        <v>1586</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1480346777153202</v>
+        <v>0.1103597356015969</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1366736544747824</v>
+        <v>0.05066615746607198</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2493,29 +2496,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>638</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3687277122325638</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3857020660410981</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>978</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.5841024853737995</v>
+        <v>0.2414902277807456</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2571,34 +2576,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>38012</v>
+        <v>36104</v>
       </c>
       <c r="M4" t="n">
-        <v>963</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P4" t="n">
-        <v>829</v>
+        <v>77</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1481278166620073</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.1055945425444167</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2608,38 +2613,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.3030216391542161</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3432461105733071</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4347647734522189</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03107911193036562</v>
+        <v>-0.01461330875779881</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.06570607307834775</v>
+        <v>0.03866911824740316</v>
       </c>
       <c r="AH4" t="n">
-        <v>-598</v>
+        <v>-11</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2694,34 +2701,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36669</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>36714</v>
+        <v>36486</v>
       </c>
       <c r="M5" t="n">
-        <v>73</v>
+        <v>341</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.08468994349340253</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1063946936086794</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="P5" t="n">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.05685813031137536</v>
+        <v>0.1248757608764939</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.01122987103820594</v>
+        <v>0.1117576504968426</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2731,38 +2738,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-596</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.08468994349340253</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1063946936086794</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>310</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>255</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.09252596198563912</v>
+        <v>0.2414902277807456</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1254437834365764</v>
+        <v>0.06109149303077064</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2840377687391613</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-947</v>
+        <v>252</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2821,34 +2830,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38965</v>
+        <v>36119</v>
       </c>
       <c r="M6" t="n">
-        <v>1621</v>
+        <v>89</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.3438943005195566</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3594525369392275</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="P6" t="n">
-        <v>1605</v>
+        <v>87</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1435933286470068</v>
+        <v>0.1062085773759145</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.132777969374361</v>
+        <v>0.04876036061740716</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2858,50 +2867,52 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3438943005195566</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3594525369392275</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1038</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.5241446626540196</v>
+        <v>0.2414902277807456</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.003895685100421348</v>
+        <v>-0.00190579684866482</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02483341171300724</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.02718342682994428</v>
+        <v>0.01270751190913399</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.04087266136534051</v>
+        <v>-0.03866911824740316</v>
       </c>
       <c r="AL6" t="n">
-        <v>658</v>
+        <v>11</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
@@ -2952,76 +2963,80 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37691</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>36167</v>
+      </c>
       <c r="M7" t="n">
-        <v>1896</v>
+        <v>120</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.5118647638611962</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.5306006583632554</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="P7" t="n">
-        <v>1860</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.3227777145631379</v>
+        <v>0.1145559160383216</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.3227777145631379</v>
+        <v>0.06098124266883433</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.180068479284433</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>742</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.5118647638611962</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.5306006583632554</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1154</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>34</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>1.048612609714667</v>
+        <v>0.2414902277807456</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.1861040600883555</v>
+        <v>0.01031508520276235</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-0.1431370516286323</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>31</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -3077,34 +3092,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>39220</v>
+        <v>36119</v>
       </c>
       <c r="M8" t="n">
-        <v>1797</v>
+        <v>89</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4312992530526795</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4447848555707743</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="P8" t="n">
-        <v>1777</v>
+        <v>87</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.2234641670620525</v>
+        <v>0.1064291866548168</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.2175550011485047</v>
+        <v>0.04886164234305112</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -3114,50 +3129,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X8" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.4312992530526795</v>
+        <v>-0.194516414529035</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.4447848555707743</v>
+        <v>-0.1963378406814934</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1214</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.7583940330091237</v>
+        <v>0.2414902277807456</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.08088134667372232</v>
+        <v>-0.001804515123020864</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-0.06257154082011562</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>236</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1119604586040879</v>
+        <v>0.01280879363477794</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.1282776138984634</v>
+        <v>-0.03866911824740316</v>
       </c>
       <c r="AL8" t="n">
-        <v>834</v>
+        <v>11</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -3208,75 +3225,73 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>36811</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>36971</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.08338363561412487</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.09913795911208834</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.02535509152894382</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.009222918648725712</v>
+        <v>0</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-497</v>
+        <v>-31</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.08338363561412487</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.09913795911208834</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>109</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-55</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.09096895806566918</v>
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1274507358260566</v>
+        <v>-0.05066615746607198</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.285344076618439</v>
+        <v>0.194516414529035</v>
       </c>
       <c r="AH9" t="n">
-        <v>-869</v>
+        <v>-58</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3286,10 +3301,10 @@
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="n">
-        <v>0.05726299061600626</v>
+        <v>0.09998223277219531</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.04676350711538768</v>
+        <v>-0.0814831053233861</v>
       </c>
     </row>
     <row r="10">
@@ -3339,34 +3354,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>38975</v>
+        <v>36104</v>
       </c>
       <c r="M10" t="n">
-        <v>1629</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.3693757033282531</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.3885025197646095</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="P10" t="n">
-        <v>1581</v>
+        <v>77</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.1547427722681643</v>
+        <v>0.08381851803583454</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.1434400770631561</v>
+        <v>0.03605284870827317</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -3376,59 +3391,61 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X10" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.3693757033282531</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.3885025197646095</v>
+        <v>-0.1558472962816319</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1046</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-8</v>
+      </c>
       <c r="AD10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.5857302125492334</v>
+        <v>0.1846197916504295</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.006766422588373733</v>
+        <v>-0.01461330875779881</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>-0.0006479910956892487</v>
+        <v>0.03866911824740316</v>
       </c>
       <c r="AH10" t="n">
-        <v>68</v>
+        <v>-11</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.03784553451873936</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.066354064174037</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>666</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.05726299061600626</v>
+        <v>0.09998223277219531</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-0.05537205093104502</v>
+        <v>-0.01738466379486436</v>
       </c>
     </row>
   </sheetData>
@@ -3726,68 +3743,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441412</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027516</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.503509252857314</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2352416489517779</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1561727120528913</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459927</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.503509252857314</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441412</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616547</v>
+        <v>0.9463998245842122</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3835,34 +3850,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37538</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38957</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1615</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3701203966363426</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.385702066041098</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1590</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.14808047344038</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.136709692353978</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39877</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>41394</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1398</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.6157753345140465</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.6157753345140465</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1397</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2811987286404189</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.2002379359033743</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3872,31 +3887,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>353</v>
+        <v>637</v>
       </c>
       <c r="X3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.3701203966363426</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.6157753345140465</v>
+        <v>-0.385702066041098</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1045</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>185</v>
-      </c>
+        <v>978</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1.602643947220921</v>
+        <v>0.5876049877783638</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3952,34 +3965,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="M4" t="n">
+        <v>962</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.3013243461981798</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.343246110573307</v>
+      </c>
+      <c r="P4" t="n">
+        <v>813</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1482043849238123</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.1056221565201652</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40911</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1067</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1066</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1974000942251041</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.1228166173480004</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3989,40 +4002,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3013243461981798</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.343246110573307</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>712</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-148</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.4312792989973724</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.07742131855537387</v>
+        <v>-0.03108753583381273</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1599778535892008</v>
+        <v>0.06879605043816273</v>
       </c>
       <c r="AH4" t="n">
-        <v>-333</v>
+        <v>-598</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4077,34 +4088,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>36669</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>36791</v>
+      </c>
+      <c r="M5" t="n">
+        <v>126</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.08670925919127181</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1063946936086794</v>
+      </c>
+      <c r="P5" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.05007226437034398</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.01295925171522207</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>40763</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.1370507850170346</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.1839140978547308</v>
-      </c>
-      <c r="P5" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.05447624842016547</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.03609137375178511</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4114,40 +4125,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>965</v>
+        <v>41</v>
       </c>
       <c r="X5" t="n">
-        <v>610</v>
+        <v>-596</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1370507850170346</v>
+        <v>-0.08670925919127181</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1839140978547308</v>
+        <v>-0.1063946936086794</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>245</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-615</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1588167445285178</v>
+        <v>0.09494157261956904</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1641465621515892</v>
+        <v>-0.1237504406387559</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.4787245494970119</v>
+        <v>0.2834111374450707</v>
       </c>
       <c r="AH5" t="n">
-        <v>-800</v>
+        <v>-893</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4156,12 +4165,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.1156075488991724</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.08239734478042915</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4210,34 +4215,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>38972</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3453417712744165</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3594525369392275</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1434249681573835</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.13282073104408</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40981</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1115</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.4557974809248457</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1114</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1964706599294577</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1249550898052054</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -4247,62 +4252,56 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3453417712744165</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4557974809248457</v>
+        <v>-0.3594525369392275</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>760</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-100</v>
-      </c>
+        <v>1043</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.8375512147563215</v>
+        <v>0.5275145963515799</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0752828460981689</v>
+        <v>-0.003888961309897937</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1599778535892008</v>
+        <v>0.0247786253619261</v>
       </c>
       <c r="AH6" t="n">
-        <v>-285</v>
+        <v>65</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.002138472457204971</v>
+        <v>0.02719857452391479</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.04401742507623663</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>663</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.1156075488991724</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>0.005169824131459944</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4347,80 +4346,76 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37691</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.5129416657678356</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.5306006583632555</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1863</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.3228628240476925</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.3228628240476925</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>39833</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40581</v>
-      </c>
-      <c r="M7" t="n">
-        <v>839</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.345107623352002</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.345107623352002</v>
-      </c>
-      <c r="P7" t="n">
-        <v>838</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.189327538515464</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1044666291326852</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>-0.1818773751653308</v>
+      </c>
       <c r="W7" t="n">
-        <v>322</v>
+        <v>741</v>
       </c>
       <c r="X7" t="n">
-        <v>-33</v>
+        <v>104</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.345107623352002</v>
+        <v>-0.5129416657678356</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.345107623352002</v>
+        <v>-0.5306006583632555</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>517</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-343</v>
-      </c>
+        <v>1154</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.5269684541426505</v>
+        <v>1.053142159196343</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.0957713067706891</v>
+        <v>0.1861531316937145</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2706677111620446</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-528</v>
-      </c>
+        <v>-0.1428212691314931</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -4476,34 +4471,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>39232</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1803</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.4325538949497473</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.4447848555707743</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1788</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.2230983505730857</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.2176183231516953</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>41131</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1220</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.5035314930286399</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.5035314930286399</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1219</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2326687227146711</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.1547818336960466</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4513,52 +4508,50 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.5035314930286399</v>
+        <v>-0.4325538949497473</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.5035314930286399</v>
+        <v>-0.4447848555707743</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>865</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5</v>
-      </c>
+        <v>1221</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1.014226453356259</v>
+        <v>0.7622818997258614</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.04545610220732765</v>
+        <v>0.08090863079771735</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1122438414854067</v>
+        <v>-0.06243349831340472</v>
       </c>
       <c r="AH8" t="n">
-        <v>-180</v>
+        <v>243</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.03196521634804622</v>
+        <v>0.1119961666315301</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.04773401210379413</v>
+        <v>-0.1312295487515674</v>
       </c>
       <c r="AL8" t="n">
-        <v>153</v>
+        <v>841</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -4609,34 +4602,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>36811</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>36972</v>
+      </c>
+      <c r="M9" t="n">
+        <v>250</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.08359195134453035</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.09913795911208823</v>
+      </c>
+      <c r="P9" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.02537765948076364</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.009233561793082153</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>40420</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>41338</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1359</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2571591117823077</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2571591117823077</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1358</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1505332319931552</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.1056880755753982</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4646,40 +4639,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>728</v>
+        <v>140</v>
       </c>
       <c r="X9" t="n">
-        <v>373</v>
+        <v>-497</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2571591117823077</v>
+        <v>-0.08359195134453035</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2571591117823077</v>
+        <v>-0.09913795911208823</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>631</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-229</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3461833023210568</v>
+        <v>0.09121695457299217</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09454986032797609</v>
+        <v>-0.1274761305608958</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.3586162227317389</v>
+        <v>0.2865284452918122</v>
       </c>
       <c r="AH9" t="n">
-        <v>-414</v>
+        <v>-868</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4688,8 +4679,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.05960063366693302</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.04865028496396862</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4738,34 +4733,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>38973</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1626</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.3678399968604835</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.3885025197646093</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1570</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.154881498180703</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.1434743120189312</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>41117</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1210</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4970589048573092</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4970589048573092</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1209</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.2336732417091007</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1548122080152736</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -4775,58 +4770,60 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.4970589048573092</v>
+        <v>-0.3678399968604835</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.4970589048573092</v>
+        <v>-0.3885025197646093</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>855</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-5</v>
-      </c>
+        <v>1044</v>
+      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.9883044150852045</v>
+        <v>0.5818779977120792</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.04542572788810068</v>
+        <v>0.006764619664953231</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.1187164296567373</v>
+        <v>0.002280399775859032</v>
       </c>
       <c r="AH10" t="n">
-        <v>-190</v>
+        <v>66</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.0319955906672732</v>
+        <v>0.03785215549876596</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.04126142393246346</v>
+        <v>-0.06651565066230369</v>
       </c>
       <c r="AL10" t="n">
-        <v>143</v>
+        <v>664</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.05960063366693302</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>-0.05974576872210891</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5123,34 +5120,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.08269444253856417</v>
+        <v>0.2352416489517779</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.0521896337568788</v>
+        <v>0.1562010221613542</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5160,22 +5157,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.1954368693665688</v>
+        <v>-0.503509252857314</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2022979914860074</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5184,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160741</v>
+        <v>1.014136226616547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5232,34 +5229,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39877</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43557</v>
+        <v>41394</v>
       </c>
       <c r="M3" t="n">
-        <v>131</v>
+        <v>1398</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="P3" t="n">
-        <v>130</v>
+        <v>1397</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.2811987286404189</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.03825741284413761</v>
+        <v>0.2002742339070991</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5269,31 +5266,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>353</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.6157753345140465</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>67</v>
+        <v>1045</v>
       </c>
       <c r="AC3" t="n">
-        <v>-9</v>
+        <v>185</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>1.602643947220921</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -5349,34 +5346,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43545</v>
+        <v>40911</v>
       </c>
       <c r="M4" t="n">
-        <v>123</v>
+        <v>1067</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="P4" t="n">
-        <v>119</v>
+        <v>1066</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04899572133157781</v>
+        <v>0.1974000942251041</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02899795472484739</v>
+        <v>0.1228388808517359</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -5386,40 +5383,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1425767900867722</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1452798889626855</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>59</v>
+        <v>712</v>
       </c>
       <c r="AC4" t="n">
-        <v>-17</v>
+        <v>-148</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1662852001652733</v>
+        <v>0.8375512147563215</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.009259458119290218</v>
+        <v>-0.07743535305536324</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03785011884304235</v>
+        <v>0.1599778535892008</v>
       </c>
       <c r="AH4" t="n">
-        <v>-8</v>
+        <v>-333</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5474,34 +5471,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>40763</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43557</v>
+        <v>41117</v>
       </c>
       <c r="M5" t="n">
-        <v>131</v>
+        <v>1210</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1370507850170346</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1839140978547308</v>
       </c>
       <c r="P5" t="n">
-        <v>130</v>
+        <v>267</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.05447624842016547</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.03825741284413761</v>
+        <v>0.03609791619247182</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -5511,40 +5508,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>965</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1370507850170346</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.1839140978547308</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>67</v>
+        <v>245</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9</v>
+        <v>-615</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>0.1588167445285178</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.1641763177146273</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.4787245494970119</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5553,8 +5550,12 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1156075488991724</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.08239734478042915</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5603,34 +5604,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>43557</v>
+        <v>40981</v>
       </c>
       <c r="M6" t="n">
-        <v>131</v>
+        <v>1115</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="P6" t="n">
-        <v>130</v>
+        <v>1114</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.06265132539194433</v>
+        <v>0.1964706599294577</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.03825741284413761</v>
+        <v>0.1249777409591674</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -5640,58 +5641,62 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1804269089298145</v>
+        <v>-0.4557974809248457</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>67</v>
+        <v>760</v>
       </c>
       <c r="AC6" t="n">
-        <v>-9</v>
+        <v>-100</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2201474290648269</v>
+        <v>0.8375512147563215</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-0.07529649294793174</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
+        <v>0.1599778535892008</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-285</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.009259458119290218</v>
+        <v>0.002138860107431501</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.03785011884304235</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.1156075488991724</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>0.005169824131459944</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5736,34 +5741,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43700</v>
+        <v>39833</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43794</v>
+        <v>40581</v>
       </c>
       <c r="M7" t="n">
-        <v>296</v>
+        <v>839</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1075633435564417</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1293912896026904</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="P7" t="n">
-        <v>271</v>
+        <v>838</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.06204575334585839</v>
+        <v>0.189327538515464</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05683143938603525</v>
+        <v>0.1044855662540467</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5773,40 +5778,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>231</v>
+        <v>322</v>
       </c>
       <c r="X7" t="n">
-        <v>167</v>
+        <v>-33</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1075633435564417</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1293912896026904</v>
+        <v>-0.345107623352002</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>65</v>
+        <v>517</v>
       </c>
       <c r="AC7" t="n">
-        <v>-11</v>
+        <v>-343</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1205277066779076</v>
+        <v>0.5269684541426505</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.01857402654189764</v>
+        <v>-0.09578866765305245</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.0728635653733728</v>
+        <v>0.2706677111620446</v>
       </c>
       <c r="AH7" t="n">
-        <v>-2</v>
+        <v>-528</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5865,34 +5870,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>43560</v>
+        <v>41131</v>
       </c>
       <c r="M8" t="n">
-        <v>134</v>
+        <v>1220</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="P8" t="n">
-        <v>133</v>
+        <v>1219</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.05500203465183429</v>
+        <v>0.2326687227146711</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.0339659689750515</v>
+        <v>0.1548098916739253</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -5902,52 +5907,52 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.5035314930286399</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>70</v>
+        <v>865</v>
       </c>
       <c r="AC8" t="n">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1824558496074078</v>
+        <v>1.014226453356259</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.004291443869086108</v>
+        <v>-0.04546434223317389</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02612444624760468</v>
+        <v>0.1122438414854067</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>-180</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.004968014250204111</v>
+        <v>0.03197101082218935</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01172567259543766</v>
+        <v>-0.04773401210379413</v>
       </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
@@ -5998,34 +6003,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43700</v>
+        <v>40420</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43773</v>
+        <v>41338</v>
       </c>
       <c r="M9" t="n">
-        <v>281</v>
+        <v>1359</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.0852956681697401</v>
+        <v>-0.2571591117823077</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1293912896026903</v>
+        <v>-0.2571591117823077</v>
       </c>
       <c r="P9" t="n">
-        <v>229</v>
+        <v>1358</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.06270003647641897</v>
+        <v>0.1505332319931552</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05596167650303357</v>
+        <v>0.1057072341136822</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6035,40 +6040,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>231</v>
+        <v>728</v>
       </c>
       <c r="X9" t="n">
-        <v>167</v>
+        <v>373</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.0852956681697401</v>
+        <v>-0.2571591117823077</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1293912896026903</v>
+        <v>-0.2571591117823077</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>50</v>
+        <v>631</v>
       </c>
       <c r="AC9" t="n">
-        <v>-26</v>
+        <v>-229</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.09324944159723114</v>
+        <v>0.3461833023210568</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.01770426365889596</v>
+        <v>-0.09456699979341698</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.0951312407600744</v>
+        <v>0.3586162227317389</v>
       </c>
       <c r="AH9" t="n">
-        <v>-17</v>
+        <v>-414</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -6127,34 +6132,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>43557</v>
+        <v>41117</v>
       </c>
       <c r="M10" t="n">
-        <v>131</v>
+        <v>1210</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="P10" t="n">
-        <v>130</v>
+        <v>1209</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.05456634024302426</v>
+        <v>0.2336732417091007</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.0333203965440686</v>
+        <v>0.1548402714992375</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -6164,52 +6169,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1543024626822098</v>
+        <v>-0.4970589048573092</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>67</v>
+        <v>855</v>
       </c>
       <c r="AC10" t="n">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.1824558496074078</v>
+        <v>0.9883044150852045</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.004937016300069007</v>
+        <v>-0.04543396240786163</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.02612444624760468</v>
+        <v>0.1187164296567373</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-190</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.004322441819221211</v>
+        <v>0.03200139064750161</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01172567259543766</v>
+        <v>-0.04126142393246346</v>
       </c>
       <c r="AL10" t="n">
-        <v>8</v>
+        <v>143</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -6512,34 +6517,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606706</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2022979914860074</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428352</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05211846719049091</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348785</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425155</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440421</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -6549,22 +6554,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.1989728318606706</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348785</v>
+        <v>-0.2022979914860074</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -6573,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986547</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -6621,34 +6626,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>134</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="P3" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06424234517826913</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.03961631664809385</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M3" t="n">
-        <v>122</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="P3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1330355594692814</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.06776900748902423</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -6658,31 +6663,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC3" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.2239202664496773</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6738,34 +6743,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43545</v>
+      </c>
+      <c r="M4" t="n">
+        <v>124</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1419538085967058</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1452798889626854</v>
+      </c>
+      <c r="P4" t="n">
+        <v>118</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04879934490473427</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02895708373240715</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44061</v>
-      </c>
-      <c r="M4" t="n">
-        <v>126</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P4" t="n">
-        <v>125</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1183626651723915</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.0612671142774218</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6775,40 +6780,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1419538085967058</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1452798889626854</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="AC4" t="n">
-        <v>48</v>
+        <v>-19</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.1654384228016292</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.006501893211602432</v>
+        <v>-0.0106592329156867</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.02657434774935885</v>
+        <v>0.04099950346766634</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -6863,76 +6868,80 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M5" t="n">
+        <v>134</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="P5" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.06424234517826913</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.03961631664809385</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>473</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="P5" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.2529670961922015</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.2529670961922015</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>-0.2560188779564279</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-9</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.2239202664496773</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.1851980887031773</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
       <c r="AI5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
@@ -6988,34 +6997,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M6" t="n">
+        <v>134</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1829533120643722</v>
+      </c>
+      <c r="P6" t="n">
+        <v>133</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06424234517826913</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.03961631664809385</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44075</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3225249683879728</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1413753176102969</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.07600544504741392</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7025,49 +7034,49 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3225249683879728</v>
+        <v>-0.1829533120643722</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="AC6" t="n">
-        <v>58</v>
+        <v>-9</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4760691587711159</v>
+        <v>0.2239202664496773</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.008236437558389695</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.01473833076999213</v>
+        <v>0.0106592329156867</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.02657434774935885</v>
+        <v>-0.04099950346766634</v>
       </c>
       <c r="AL6" t="n">
         <v>10</v>
@@ -7121,34 +7130,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43700</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43794</v>
+      </c>
+      <c r="M7" t="n">
+        <v>297</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1103143547728899</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1293912896026903</v>
+      </c>
+      <c r="P7" t="n">
+        <v>276</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.06265137792267675</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05740167726782903</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44132</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44182</v>
-      </c>
-      <c r="M7" t="n">
-        <v>211</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.03342944898032829</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1039580150464059</v>
-      </c>
-      <c r="P7" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.05227328617519215</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.03495896469905611</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7158,40 +7167,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="X7" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.03342944898032829</v>
+        <v>-0.1103143547728899</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1039580150464059</v>
+        <v>-0.1293912896026903</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="AC7" t="n">
-        <v>-20</v>
+        <v>-13</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.03458562744857296</v>
+        <v>0.1239925083254882</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03281004278996812</v>
+        <v>0.01778536061973519</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2890955194076446</v>
+        <v>0.07263895729148229</v>
       </c>
       <c r="AH7" t="n">
-        <v>-64</v>
+        <v>-4</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7200,12 +7209,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.02722714751693389</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>-0.02590251273381827</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -7254,34 +7259,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>43563</v>
+      </c>
+      <c r="M8" t="n">
+        <v>136</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1569093966243399</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1569093966243399</v>
+      </c>
+      <c r="P8" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.05701313870447648</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.03541775730074802</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44054</v>
-      </c>
-      <c r="M8" t="n">
-        <v>121</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.295950620638614</v>
-      </c>
-      <c r="P8" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1200990891921226</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.06092989901287445</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -7291,62 +7296,58 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.295950620638614</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="AC8" t="n">
-        <v>43</v>
+        <v>-7</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4203549201436105</v>
+        <v>0.186112140256443</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.006839108476149776</v>
+        <v>-0.00419855934734583</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02657434774935885</v>
+        <v>0.02604391544003226</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-0.0003372152645473442</v>
+        <v>0.006460673568340868</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>-0.01495558802763408</v>
       </c>
       <c r="AL8" t="n">
-        <v>-5</v>
+        <v>12</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="n">
-        <v>0.02722714751693389</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.006765434017745875</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7391,76 +7392,80 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43700</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43773</v>
+      </c>
+      <c r="M9" t="n">
+        <v>282</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.088115321372497</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1293912896026904</v>
+      </c>
+      <c r="P9" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.06322404768423408</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05644966093982831</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>43889</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>473</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.133157003329941</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.133157003329941</v>
-      </c>
-      <c r="P9" t="n">
-        <v>473</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.07510591457190988</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.07510591457190988</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.1140611994265254</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>232</v>
       </c>
       <c r="X9" t="n">
-        <v>-16</v>
+        <v>167</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.133157003329941</v>
+        <v>-0.088115321372497</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.133157003329941</v>
+        <v>-0.1293912896026904</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>466</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-28</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1536114427196829</v>
+        <v>0.09662989568496894</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.007336907082885646</v>
+        <v>0.01683334429173446</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1893679650580319</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0.09483799069187515</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-19</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -7516,34 +7521,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>43913</v>
+        <v>43458</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>44070</v>
+        <v>43558</v>
       </c>
       <c r="M10" t="n">
         <v>133</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="P10" t="n">
         <v>132</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.129013665335106</v>
+        <v>0.05652127533734484</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.06859602378329933</v>
+        <v>0.03472563333817768</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>44564</v>
+        <v>43880</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -7553,52 +7558,52 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.309428832058098</v>
+        <v>-0.1569093966243399</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="AC10" t="n">
-        <v>55</v>
+        <v>-10</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.4480766739513375</v>
+        <v>0.186112140256443</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.0008270162942751041</v>
+        <v>-0.004890683309916169</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.01309613632987483</v>
+        <v>0.02604391544003226</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.007328909505877536</v>
+        <v>0.005768549605770529</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.01347821141948402</v>
+        <v>-0.01495558802763408</v>
       </c>
       <c r="AL10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
@@ -7901,34 +7906,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348785</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425155</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440421</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428741</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996986</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694572</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7938,22 +7943,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428741</v>
+        <v>-0.2902196151348785</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7962,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088524</v>
+        <v>0.4088864968986547</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8010,34 +8015,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M3" t="n">
+        <v>122</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="P3" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1330355594692814</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.06776900748902423</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45092</v>
-      </c>
-      <c r="M3" t="n">
-        <v>364</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.3287615049188402</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.3287615049188402</v>
-      </c>
-      <c r="P3" t="n">
-        <v>363</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2035103799588042</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.138770824610914</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8047,31 +8052,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3287615049188402</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53</v>
+        <v>44</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4897834485477317</v>
+        <v>0.4760691587711159</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8127,34 +8132,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44061</v>
+      </c>
+      <c r="M4" t="n">
+        <v>126</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P4" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1183626651723915</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.0612671142774218</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45135</v>
-      </c>
-      <c r="M4" t="n">
-        <v>393</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2377598766809245</v>
-      </c>
-      <c r="P4" t="n">
-        <v>392</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1318162553441144</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.09338610296468229</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -8164,40 +8169,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2377598766809245</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="AC4" t="n">
-        <v>-22</v>
+        <v>48</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3119225417387239</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.04538472164623171</v>
+        <v>-0.006501893211602432</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.09100162823791569</v>
+        <v>0.02657434774935885</v>
       </c>
       <c r="AH4" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8252,91 +8257,83 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>473</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="P5" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.2529670961922015</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.2529670961922015</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45324</v>
-      </c>
-      <c r="M5" t="n">
-        <v>523</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.284273346248364</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2944681800461371</v>
-      </c>
-      <c r="P5" t="n">
-        <v>498</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1768584148512431</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.1444962390162962</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-      <c r="V5" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>-0.2560188779564279</v>
+      </c>
       <c r="W5" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.284273346248364</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2944681800461371</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>326</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>106</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3971814445616686</v>
+        <v>0.4760691587711159</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.005725414405382212</v>
+        <v>0.1851980887031773</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.04448815867047617</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>159</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" s="3" t="inlineStr"/>
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.7792202084776549</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.4371988460691945</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8385,34 +8382,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44075</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3225249683879728</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1413753176102969</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.07600544504741392</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44848</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45299</v>
-      </c>
-      <c r="M6" t="n">
-        <v>505</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.3157227764659216</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.3157227764659216</v>
-      </c>
-      <c r="P6" t="n">
-        <v>504</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1795628224484643</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1441640097761239</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -8422,62 +8419,58 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>197</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.3157227764659216</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3157227764659216</v>
+        <v>-0.3225249683879728</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>308</v>
+        <v>113</v>
       </c>
       <c r="AC6" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4613960038525204</v>
+        <v>0.4760691587711159</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.005393185165209868</v>
+        <v>0.008236437558389695</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.01303872845291854</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.05077790681144158</v>
+        <v>0.01473833076999213</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>-0.07796289978499715</v>
+        <v>-0.02657434774935885</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.7792202084776549</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.05986522785946014</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8522,34 +8515,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44132</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44182</v>
+      </c>
+      <c r="M7" t="n">
+        <v>211</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.03342944898032829</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1039580150464059</v>
+      </c>
+      <c r="P7" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.05227328617519215</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.03495896469905611</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44586</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45006</v>
-      </c>
-      <c r="M7" t="n">
-        <v>304</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.1208274628418153</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.1208274628418153</v>
-      </c>
-      <c r="P7" t="n">
-        <v>303</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.05571830382583604</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.03473065536389792</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8559,40 +8552,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="X7" t="n">
-        <v>-180</v>
+        <v>153</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1208274628418153</v>
+        <v>-0.03342944898032829</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1208274628418153</v>
+        <v>-0.1039580150464059</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
+        <v>35</v>
       </c>
       <c r="AC7" t="n">
-        <v>69</v>
+        <v>-20</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1374331632700618</v>
+        <v>0.03458562744857296</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.1040401692470161</v>
+        <v>-0.03281004278996812</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2079340420770248</v>
+        <v>0.2890955194076446</v>
       </c>
       <c r="AH7" t="n">
-        <v>122</v>
+        <v>-64</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8602,10 +8595,10 @@
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" s="3" t="n">
-        <v>0.06155864235340314</v>
+        <v>0.02722714751693389</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.05888323104964921</v>
+        <v>-0.02590251273381827</v>
       </c>
     </row>
     <row r="8">
@@ -8655,34 +8648,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44054</v>
+      </c>
+      <c r="M8" t="n">
+        <v>121</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.295950620638614</v>
+      </c>
+      <c r="P8" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1200990891921226</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.06092989901287445</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45078</v>
-      </c>
-      <c r="M8" t="n">
-        <v>354</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.2528925789158353</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.2528925789158353</v>
-      </c>
-      <c r="P8" t="n">
-        <v>353</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1477423324911242</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.09935375814728072</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -8692,61 +8685,61 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2528925789158353</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2528925789158353</v>
+        <v>-0.295950620638614</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="AC8" t="n">
-        <v>-61</v>
+        <v>43</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3384956055567623</v>
+        <v>0.4203549201436105</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.03941706646363329</v>
+        <v>-0.006839108476149776</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.07586892600300488</v>
+        <v>0.02657434774935885</v>
       </c>
       <c r="AH8" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.005967655182598425</v>
+        <v>-0.0003372152645473442</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01513270223491081</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-39</v>
+        <v>-5</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.06155864235340314</v>
+        <v>0.02722714751693389</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.001367825774972298</v>
+        <v>-0.006765434017745875</v>
       </c>
     </row>
     <row r="9">
@@ -8792,91 +8785,83 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43889</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>473</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.133157003329941</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.133157003329941</v>
+      </c>
+      <c r="P9" t="n">
+        <v>473</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.07510591457190988</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.07510591457190988</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>301</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.04767358453056447</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.09928531078041158</v>
-      </c>
-      <c r="P9" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.05743316925940323</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.03562307663313719</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>-0.1140611994265254</v>
+      </c>
       <c r="W9" t="n">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>102</v>
+        <v>-16</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.04767358453056447</v>
+        <v>-0.133157003329941</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.09928531078041158</v>
+        <v>-0.133157003329941</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-216</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.05006013038823931</v>
+        <v>0.1536114427196829</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1031477479777768</v>
+        <v>0.007336907082885646</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2810879203882757</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-163</v>
-      </c>
+        <v>0.1893679650580319</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.06155864235340314</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>-0.05794117449794767</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8925,34 +8910,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>44070</v>
+      </c>
+      <c r="M10" t="n">
+        <v>133</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.309428832058098</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.309428832058098</v>
+      </c>
+      <c r="P10" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.129013665335106</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.06859602378329933</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45072</v>
-      </c>
-      <c r="M10" t="n">
-        <v>351</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2460561291388812</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2460561291388812</v>
-      </c>
-      <c r="P10" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1367086738207894</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09154456676116604</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -8962,62 +8947,58 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.2460561291388812</v>
+        <v>-0.309428832058098</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.2460561291388812</v>
+        <v>-0.309428832058098</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="AC10" t="n">
-        <v>-64</v>
+        <v>55</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.3263586835155881</v>
+        <v>0.4480766739513375</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>-0.04722625784974796</v>
+        <v>0.0008270162942751041</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.08270537577995896</v>
+        <v>0.01309613632987483</v>
       </c>
       <c r="AH10" t="n">
-        <v>-11</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>-0.00184153620351625</v>
+        <v>0.007328909505877536</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.008296252457956732</v>
+        <v>-0.01347821141948402</v>
       </c>
       <c r="AL10" t="n">
-        <v>-42</v>
+        <v>7</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.06155864235340314</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>0.001697815565633309</v>
-      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9314,34 +9295,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428741</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996986</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694572</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138081</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645823</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451878</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -9351,22 +9332,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138081</v>
+        <v>-0.3239608533428741</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -9375,7 +9356,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367029</v>
+        <v>0.4792042812088524</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -9423,34 +9404,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45092</v>
+      </c>
+      <c r="M3" t="n">
+        <v>364</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3287615049188402</v>
+      </c>
+      <c r="P3" t="n">
+        <v>363</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.2035103799588042</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.138770824610914</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45840</v>
-      </c>
-      <c r="M3" t="n">
-        <v>92</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1891226670882522</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1891226670882522</v>
-      </c>
-      <c r="P3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.09126633999965644</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05961065063903417</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -9460,31 +9441,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1891226670882522</v>
+        <v>-0.3287615049188402</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>-53</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.2332321541276028</v>
+        <v>0.4897834485477317</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -9540,34 +9521,34 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="M4" t="n">
+        <v>393</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2377598766809245</v>
+      </c>
+      <c r="P4" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1318162553441144</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.09338610296468229</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M4" t="n">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="P4" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.06216000016109517</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.04927686199609638</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -9577,40 +9558,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.2377598766809245</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>102</v>
+        <v>198</v>
       </c>
       <c r="AC4" t="n">
-        <v>47</v>
+        <v>-22</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.3119225417387239</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.0103337886429378</v>
+        <v>-0.04538472164623171</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03775943918171465</v>
+        <v>0.09100162823791569</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9665,73 +9646,77 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45324</v>
+      </c>
+      <c r="M5" t="n">
+        <v>523</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.284273346248364</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2944681800461371</v>
+      </c>
+      <c r="P5" t="n">
+        <v>498</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1768584148512431</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.1444962390162962</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>88</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.284273346248364</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2944681800461371</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>106</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.3971814445616686</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.05961065063903417</v>
+        <v>0.005725414405382212</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1891226670882522</v>
+        <v>0.04448815867047617</v>
       </c>
       <c r="AH5" t="n">
-        <v>-58</v>
+        <v>159</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9741,10 +9726,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.1818988367474383</v>
+        <v>0.7792202084776549</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1368328282013731</v>
+        <v>-0.4371988460691945</v>
       </c>
     </row>
     <row r="6">
@@ -9794,34 +9779,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44848</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45299</v>
+      </c>
+      <c r="M6" t="n">
+        <v>505</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.3157227764659216</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3157227764659216</v>
+      </c>
+      <c r="P6" t="n">
+        <v>504</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1795628224484643</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1441640097761239</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45904</v>
-      </c>
-      <c r="M6" t="n">
-        <v>136</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.1513632279065376</v>
-      </c>
-      <c r="P6" t="n">
-        <v>135</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.06216000016109517</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.04927686199609638</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -9831,61 +9816,61 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3157227764659216</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1513632279065376</v>
+        <v>-0.3157227764659216</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="AC6" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1783604398064753</v>
+        <v>0.4613960038525204</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.0103337886429378</v>
+        <v>0.005393185165209868</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03775943918171465</v>
+        <v>0.01303872845291854</v>
       </c>
       <c r="AH6" t="n">
-        <v>44</v>
+        <v>141</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0</v>
+        <v>0.05077790681144158</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0</v>
+        <v>-0.07796289978499715</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="b">
         <v>0</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.1818988367474383</v>
+        <v>0.7792202084776549</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-0.05128610654981658</v>
+        <v>-0.05986522785946014</v>
       </c>
     </row>
     <row r="7">
@@ -9931,34 +9916,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44586</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45006</v>
+      </c>
+      <c r="M7" t="n">
+        <v>304</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1208274628418153</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1208274628418153</v>
+      </c>
+      <c r="P7" t="n">
+        <v>303</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.05571830382583604</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.03473065536389792</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45715</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45789</v>
-      </c>
-      <c r="M7" t="n">
-        <v>57</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.05069935962761241</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.05069935962761241</v>
-      </c>
-      <c r="P7" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.0411549593364987</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.02122794368812943</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -9968,40 +9953,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="X7" t="n">
-        <v>-28</v>
+        <v>-180</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.05069935962761241</v>
+        <v>-0.1208274628418153</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.05069935962761241</v>
+        <v>-0.1208274628418153</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>51</v>
+        <v>289</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4</v>
+        <v>69</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.05340706354914526</v>
+        <v>0.1374331632700618</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.03838270695090474</v>
+        <v>-0.1040401692470161</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1384233074606398</v>
+        <v>0.2079340420770248</v>
       </c>
       <c r="AH7" t="n">
-        <v>-7</v>
+        <v>122</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -10010,8 +9995,12 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>-0.05888323104964921</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10060,34 +10049,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45078</v>
+      </c>
+      <c r="M8" t="n">
+        <v>354</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2528925789158353</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.2528925789158353</v>
+      </c>
+      <c r="P8" t="n">
+        <v>353</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1477423324911242</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.09935375814728072</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45834</v>
-      </c>
-      <c r="M8" t="n">
-        <v>88</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1655864927329398</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1655864927329398</v>
-      </c>
-      <c r="P8" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.07789842917453209</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.04977318780261538</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -10097,58 +10086,62 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1655864927329398</v>
+        <v>-0.2528925789158353</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1655864927329398</v>
+        <v>-0.2528925789158353</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1</v>
+        <v>-61</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1984465631138719</v>
+        <v>0.3384956055567623</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.009837462836418794</v>
+        <v>-0.03941706646363329</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.02353617435531241</v>
+        <v>0.07586892600300488</v>
       </c>
       <c r="AH8" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.0004963258065190032</v>
+        <v>0.005967655182598425</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>-0.01422326482640224</v>
+        <v>-0.01513270223491081</v>
       </c>
       <c r="AL8" t="n">
-        <v>-48</v>
+        <v>-39</v>
       </c>
       <c r="AM8" t="b">
         <v>0</v>
       </c>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>0.001367825774972298</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10193,34 +10186,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44995</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>301</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.04767358453056447</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.09928531078041158</v>
+      </c>
+      <c r="P9" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.05743316925940323</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.03562307663313719</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45729</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="M9" t="n">
-        <v>123</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.1262973638890311</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.1262973638890311</v>
-      </c>
-      <c r="P9" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.08197862198921514</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.06182771688674071</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -10230,40 +10223,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="X9" t="n">
-        <v>-18</v>
+        <v>102</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1262973638890311</v>
+        <v>-0.04767358453056447</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1262973638890311</v>
+        <v>-0.09928531078041158</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>52</v>
+        <v>-216</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1445541751495758</v>
+        <v>0.05006013038823931</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.002217066247706533</v>
+        <v>-0.1031477479777768</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06282530319922108</v>
+        <v>0.2810879203882757</v>
       </c>
       <c r="AH9" t="n">
-        <v>49</v>
+        <v>-163</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10272,8 +10265,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.05794117449794767</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10322,34 +10319,34 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45072</v>
+      </c>
+      <c r="M10" t="n">
+        <v>351</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.2460561291388812</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.2460561291388812</v>
+      </c>
+      <c r="P10" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.1367086738207894</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.09154456676116604</v>
+      </c>
+      <c r="S10" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45881</v>
-      </c>
-      <c r="M10" t="n">
-        <v>120</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1821196302820544</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1821196302820544</v>
-      </c>
-      <c r="P10" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.0879394682295679</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.06551613565424978</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T10" t="b">
         <v>0</v>
@@ -10359,58 +10356,62 @@
       </c>
       <c r="V10" s="3" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>-0.1821196302820544</v>
+        <v>-0.2460561291388812</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>-0.1821196302820544</v>
+        <v>-0.2460561291388812</v>
       </c>
       <c r="AA10" t="b">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="AC10" t="n">
-        <v>31</v>
+        <v>-64</v>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>0.2226727000977664</v>
+        <v>0.3263586835155881</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>0.005905485015215609</v>
+        <v>-0.04722625784974796</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>0.007003036806197849</v>
+        <v>0.08270537577995896</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>-11</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.01623927365815341</v>
+        <v>-0.00184153620351625</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>-0.0307564023755168</v>
+        <v>-0.008296252457956732</v>
       </c>
       <c r="AL10" t="n">
-        <v>-16</v>
+        <v>-42</v>
       </c>
       <c r="AM10" t="b">
         <v>0</v>
       </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="n">
+        <v>0.06155864235340314</v>
+      </c>
+      <c r="AO10" s="3" t="n">
+        <v>0.001697815565633309</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10423,7 +10424,1400 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645823</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451878</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138081</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367029</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="M3" t="n">
+        <v>92</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="P3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.09126633999965644</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05961065063903417</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1891226670882522</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.2332321541276028</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>136</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="P4" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.04927686199609638</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0.1783604398064753</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.0103337886429378</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.03775943918171465</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>89</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>-0.05961065063903417</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.1891226670882522</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-58</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.1818988367474383</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>-0.1368328282013731</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_changepoint_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="M6" t="n">
+        <v>136</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="P6" t="n">
+        <v>135</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.06216000016109517</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.04927686199609638</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>-0.1513632279065376</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0.1783604398064753</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.0103337886429378</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.03775943918171465</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="3" t="n">
+        <v>0.1818988367474383</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.05128610654981658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45715</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45789</v>
+      </c>
+      <c r="M7" t="n">
+        <v>57</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="P7" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.0411549593364987</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.02122794368812943</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-28</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.05069935962761241</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.05340706354914526</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>-0.03838270695090474</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.1384233074606398</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_hmm_gspc_hrp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>45834</v>
+      </c>
+      <c r="M8" t="n">
+        <v>88</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="P8" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.07789842917453209</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.04977318780261538</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>-0.1655864927329398</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>54</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0.1984465631138719</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.009837462836418794</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.02353617435531241</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="n">
+        <v>0.0004963258065190032</v>
+      </c>
+      <c r="AK8" s="3" t="n">
+        <v>-0.01422326482640224</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AM8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45729</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="M9" t="n">
+        <v>123</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="P9" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.08197862198921514</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.06182771688674071</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>16</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.1262973638890311</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>107</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>52</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.1445541751495758</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.002217066247706533</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.06282530319922108</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>49</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>xgb</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout_wasserstein_gspc_vix_hrp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xgb_t_10_holdout</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="M10" t="n">
+        <v>120</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="P10" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>0.0879394682295679</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.06551613565424978</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="inlineStr"/>
+      <c r="W10" t="n">
+        <v>34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>-0.1821196302820544</v>
+      </c>
+      <c r="AA10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>86</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>31</v>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>0.2226727000977664</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>0.005905485015215609</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0.007003036806197849</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="n">
+        <v>0.01623927365815341</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>-0.0307564023755168</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AM10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10529,24 +11923,22 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>373</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="3" t="n">
-        <v>0.496398891966759</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -10577,20 +11969,20 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-131</v>
+        <v>155</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>523</v>
+        <v>373</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.7274709302325582</v>
+        <v>0.4963948973932335</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -10623,20 +12015,24 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>-131</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>523</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.7274709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -10672,16 +12068,14 @@
         <v>0</v>
       </c>
       <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" s="3" t="n">
-        <v>0.7540983606557377</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -10711,24 +12105,22 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-442</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>-174</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>0.2787524366471735</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -10759,21 +12151,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-114</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-442</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-174</v>
+      </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>442</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1</v>
+        <v>0.2787524366471735</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -10790,37 +12184,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>156</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>18</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0.08476454293628809</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -10847,27 +12239,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>81</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>0.3350290697674418</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -10894,14 +12284,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -10911,10 +12301,10 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.08485856905158069</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -10941,27 +12331,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-10</v>
+        <v>39</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0.7622950819672131</v>
+        <v>0.3350290697674418</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -10988,27 +12378,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-21</v>
+        <v>31</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>0.4892787524366471</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -11035,27 +12425,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9</v>
+        <v>-10</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -11072,37 +12462,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-35</v>
+        <v>-21</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>0.3634349030470914</v>
+        <v>0.4892787524366471</v>
       </c>
       <c r="K14" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -11119,24 +12509,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -11146,10 +12536,10 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3960755813953488</v>
+        <v>0.4719101123595505</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -11176,27 +12566,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>30</v>
+        <v>-52</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>27</v>
+        <v>317</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H16" t="b">
         <v>0</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" s="3" t="n">
-        <v>0.4206896551724138</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -11223,27 +12613,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0.8770491803278688</v>
+        <v>0.3632834165280089</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -11270,27 +12660,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-21</v>
+        <v>39</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="b">
         <v>0</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.52046783625731</v>
+        <v>0.3960755813953488</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -11317,14 +12707,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -11334,7 +12724,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" s="3" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.4178082191780822</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -11343,6 +12733,147 @@
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>0.4719101123595505</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
